--- a/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_384_C_te_d_Ivoire.xlsx
+++ b/SeaAroundUsExtraction/eez_output/regional_calculations/EEZ_384_C_te_d_Ivoire.xlsx
@@ -2,12 +2,12 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="Reb631e9880764b72"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R416b9e7a4e544918"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="Reded6abc886144e2"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R48415a26944c4425"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R98ee6bab80f148ff"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="R265beafb11dc4521"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Species" sheetId="1" r:id="R3adf42d80eca4231"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Commercial" sheetId="2" r:id="R80593e6968be4140"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Functional" sheetId="3" r:id="R70c2d95affe24739"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Missing TL" sheetId="4" r:id="R4423d29293904ca3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Validation" sheetId="5" r:id="R5e79edf6cf234bed"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Metadata" sheetId="6" r:id="Rb4daa2c176f349d9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -18,13 +18,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <x:styleSheet xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <x:numFmts count="6">
+  <x:numFmts count="4">
     <x:numFmt numFmtId="200" formatCode="0"/>
     <x:numFmt numFmtId="201" formatCode="#,##0.00"/>
     <x:numFmt numFmtId="202" formatCode="0.0000"/>
-    <x:numFmt numFmtId="203" formatCode="#,##0"/>
-    <x:numFmt numFmtId="204" formatCode="0.00%"/>
-    <x:numFmt numFmtId="205" formatCode="0.00"/>
+    <x:numFmt numFmtId="203" formatCode="0.00"/>
   </x:numFmts>
   <x:fonts count="7">
     <x:font>
@@ -184,7 +182,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="37">
+  <x:cellXfs count="35">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <x:extLst>
@@ -244,8 +242,6 @@
     <x:xf numFmtId="200" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="201" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="202" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="203" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <x:xf numFmtId="204" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1">
       <x:extLst>
         <x:ext uri="{C7286773-470A-42A8-94C5-96B5CB345126}">
@@ -253,14 +249,14 @@
         </x:ext>
       </x:extLst>
     </x:xf>
-    <x:xf numFmtId="205" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <x:xf numFmtId="203" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
   </x:cellStyles>
-  <x:dxfs count="3">
+  <x:dxfs count="1">
     <x:dxf>
       <x:font>
         <x:color rgb="FF9A3412"/>
@@ -268,28 +264,6 @@
       <x:fill>
         <x:patternFill patternType="solid">
           <x:bgColor rgb="FFFCEAD8"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
-        </x:patternFill>
-      </x:fill>
-    </x:dxf>
-    <x:dxf>
-      <x:font>
-        <x:b/>
-        <x:color rgb="FFB42318"/>
-      </x:font>
-      <x:fill>
-        <x:patternFill patternType="solid">
-          <x:bgColor rgb="FFFEE4E2"/>
         </x:patternFill>
       </x:fill>
     </x:dxf>
@@ -345,56 +319,36 @@
 </file>
 
 <file path=xl/tables/table2.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ384CommercialTable" displayName="EEZ384CommercialTable" ref="A1:O12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O12"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="2" name="EEZ384CommercialTable" displayName="EEZ384CommercialTable" ref="A1:E12" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E12"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="commercial_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table3.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ384FunctionalTable" displayName="EEZ384FunctionalTable" ref="A1:O25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:O25"/>
-  <x:tableColumns count="15">
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="3" name="EEZ384FunctionalTable" displayName="EEZ384FunctionalTable" ref="A1:E25" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:E25"/>
+  <x:tableColumns count="5">
     <x:tableColumn id="1" name="functional_group"/>
-    <x:tableColumn id="2" name="taxon_count_total"/>
-    <x:tableColumn id="3" name="taxon_count_matched"/>
-    <x:tableColumn id="4" name="catch_tonnes_total"/>
-    <x:tableColumn id="5" name="catch_tonnes_matched"/>
-    <x:tableColumn id="6" name="catch_tonnes_missing_tl"/>
-    <x:tableColumn id="7" name="catch_coverage_fraction"/>
-    <x:tableColumn id="8" name="sppr_correct"/>
-    <x:tableColumn id="9" name="ppr_correct"/>
-    <x:tableColumn id="10" name="tl_weighted_jensen"/>
-    <x:tableColumn id="11" name="sppr_jensen"/>
-    <x:tableColumn id="12" name="ppr_jensen"/>
-    <x:tableColumn id="13" name="jensen_difference"/>
-    <x:tableColumn id="14" name="jensen_ratio_correct_to_error"/>
-    <x:tableColumn id="15" name="jensen_percent_difference"/>
+    <x:tableColumn id="2" name="catch_tonnes_matched"/>
+    <x:tableColumn id="3" name="tl_weighted"/>
+    <x:tableColumn id="4" name="sppr"/>
+    <x:tableColumn id="5" name="ppr"/>
   </x:tableColumns>
   <x:tableStyleInfo name="TableStyleMedium2" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </x:table>
 </file>
 
 <file path=xl/tables/table4.xml><?xml version="1.0" encoding="utf-8"?>
-<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ384ValidationTable" displayName="EEZ384ValidationTable" ref="A1:D19" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
-  <x:autoFilter ref="A1:D19"/>
+<x:table xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="4" name="EEZ384ValidationTable" displayName="EEZ384ValidationTable" ref="A1:D17" headerRowCount="1" totalsRowCount="0" totalsRowShown="0">
+  <x:autoFilter ref="A1:D17"/>
   <x:tableColumns count="4">
     <x:tableColumn id="1" name="unit_id"/>
     <x:tableColumn id="2" name="check"/>
@@ -13692,7 +13646,7 @@
   </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R778e2e8f5bb3453e"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0a5fc42c44674b1b"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -13702,20 +13656,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="26" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -13723,660 +13667,231 @@
         <x:v>commercial_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Anchovies</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>0.4954686842</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.11</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>128.82495516931337</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>0.4954686842</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$H$2:$H$195,A2,'Species'!$U$2:$U$195))</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>63.82873102986368</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.11</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>128.82495516931337</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
-        <x:v>63.82873102986368</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Cod-likes</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>123.7776711627</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.49923870550702</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>3156.7392159589203</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>123.7776711627</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>3159.2460988594353</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$H$2:$H$195,A3,'Species'!$U$2:$U$195))</x:f>
-        <x:v>391044.124746666</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.49923870550702</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>3156.7392159589203</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>390733.82861936267</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>310.29612730332883</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1.0007941368383684</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0.0007941368383683179</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Crustaceans</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>10</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>63.42522482259999</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>3.315924727132053</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>206.97825784643496</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>63.42522482259999</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>251.26662025807448</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$H$2:$H$195,A4,'Species'!$U$2:$U$195))</x:f>
-        <x:v>15936.641880283232</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>3.315924727132053</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>206.97825784643496</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>13127.642537300208</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>2808.9993429830247</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.2139759164679933</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.2139759164679933</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Flatfishes</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>79.46006172969999</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.2338663354193593</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>171.34298770595112</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>79.46006172969999</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>188.31443922836488</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$H$2:$H$195,A5,'Species'!$U$2:$U$195))</x:f>
-        <x:v>14963.476965679709</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.2338663354193593</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>171.34298770595112</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>13614.924380066102</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>1348.5525856136064</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0990495832344138</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.09904958323441375</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Herring-likes</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>21107.9785445047</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>3.168320040575188</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>147.33978797995604</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>21107.9785445047</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>198.73386659511252</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$H$2:$H$195,A6,'Species'!$U$2:$U$195))</x:f>
-        <x:v>4194870.192156094</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>3.168320040575188</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>147.33978797995604</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>3110045.0834327834</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>1084825.1087233108</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.3488133064379602</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.34881330643796016</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Molluscs</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>308.97124966729996</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>2.000216858071436</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>10.0049945885064</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>308.97124966729996</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>10.019952574819703</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$H$2:$H$195,A7,'Species'!$U$2:$U$195))</x:f>
-        <x:v>3095.8772686491234</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>2.000216858071436</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>10.0049945885064</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>3091.255680925396</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>4.621587723727316</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0014950519144195</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.001495051914419386</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Other fishes &amp; inverts</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>27</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>113838.5320018882</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.2976047109193725</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>198.42880225209274</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>113838.5320018882</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>216.7176796554776</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$H$2:$H$195,A8,'Species'!$U$2:$U$195))</x:f>
-        <x:v>24670822.510835044</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.2976047109193725</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>198.42880225209274</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>22588843.555271205</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>2081978.9555638395</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.0921684614119167</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.0921684614119168</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Perch-likes</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>89</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>82496.3477119562</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>3.660784203038911</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>457.91429674419413</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>82496.3477119562</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>578.6729277137491</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$H$2:$H$195,A9,'Species'!$U$2:$U$195))</x:f>
-        <x:v>47738403.056169145</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>3.660784203038911</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>457.91429674419413</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>37776257.04648493</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>9962146.009684213</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.2637144806968426</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.26371448069684256</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Scorpionfishes</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>63.1564919816</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>3.544086170058039</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>350.0146078994088</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>63.1564919816</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>383.78675742417244</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$H$2:$H$195,A10,'Species'!$U$2:$U$195))</x:f>
-        <x:v>24238.62526790401</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>3.544086170058039</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>350.0146078994088</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>22105.69477724188</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>2132.930490662133</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.09648782868648</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.09648782868648012</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Sharks &amp; rays</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>28</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>1530.4755863006</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>3.9621897656700735</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>916.6209216121468</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>1530.4755863006</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>1389.033227620616</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$H$2:$H$195,A11,'Species'!$U$2:$U$195))</x:f>
-        <x:v>2125881.443433677</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>3.9621897656700735</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>916.6209216121468</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>1402865.942419747</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>723015.50101393</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.515384598878229</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.515384598878229</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Tuna &amp; billfishes</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>17</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>19950.0186193323</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.4330580056573785</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>2710.5536372874744</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>19950.0186193323</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>2718.558994772997</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$H$2:$H$195,A12,'Species'!$U$2:$U$195))</x:f>
-        <x:v>54235302.56347458</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.4330580056573785</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>2710.5536372874744</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>54075595.532584004</x:v>
       </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>159707.03089057654</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0029534030890948</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.0029534030890948364</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G12">
-    <x:cfRule type="cellIs" dxfId="1" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O12">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R0759148c50904c02"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Re6cadd55cc3b43c6"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -14386,20 +13901,10 @@
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:cols>
     <x:col min="1" max="1" width="34" hidden="0" customWidth="1"/>
-    <x:col min="2" max="2" width="22" hidden="0" customWidth="1"/>
-    <x:col min="3" max="3" width="22" hidden="0" customWidth="1"/>
+    <x:col min="2" max="2" width="18" hidden="0" customWidth="1"/>
+    <x:col min="3" max="3" width="15" hidden="0" customWidth="1"/>
     <x:col min="4" max="4" width="18" hidden="0" customWidth="1"/>
     <x:col min="5" max="5" width="18" hidden="0" customWidth="1"/>
-    <x:col min="6" max="6" width="18" hidden="0" customWidth="1"/>
-    <x:col min="7" max="7" width="16" hidden="0" customWidth="1"/>
-    <x:col min="8" max="8" width="18" hidden="0" customWidth="1"/>
-    <x:col min="9" max="9" width="18" hidden="0" customWidth="1"/>
-    <x:col min="10" max="10" width="15" hidden="0" customWidth="1"/>
-    <x:col min="11" max="11" width="18" hidden="0" customWidth="1"/>
-    <x:col min="12" max="12" width="18" hidden="0" customWidth="1"/>
-    <x:col min="13" max="13" width="18" hidden="0" customWidth="1"/>
-    <x:col min="14" max="14" width="16" hidden="0" customWidth="1"/>
-    <x:col min="15" max="15" width="16" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="32" customHeight="1">
@@ -14407,1362 +13912,478 @@
         <x:v>functional_group</x:v>
       </x:c>
       <x:c r="B1" s="29" t="str">
-        <x:v>taxon_count_total</x:v>
+        <x:v>catch_tonnes_matched</x:v>
       </x:c>
       <x:c r="C1" s="29" t="str">
-        <x:v>taxon_count_matched</x:v>
+        <x:v>tl_weighted</x:v>
       </x:c>
       <x:c r="D1" s="29" t="str">
-        <x:v>catch_tonnes_total</x:v>
+        <x:v>sppr</x:v>
       </x:c>
       <x:c r="E1" s="29" t="str">
-        <x:v>catch_tonnes_matched</x:v>
-      </x:c>
-      <x:c r="F1" s="29" t="str">
-        <x:v>catch_tonnes_missing_tl</x:v>
-      </x:c>
-      <x:c r="G1" s="29" t="str">
-        <x:v>catch_coverage_fraction</x:v>
-      </x:c>
-      <x:c r="H1" s="29" t="str">
-        <x:v>sppr_correct</x:v>
-      </x:c>
-      <x:c r="I1" s="29" t="str">
-        <x:v>ppr_correct</x:v>
-      </x:c>
-      <x:c r="J1" s="29" t="str">
-        <x:v>tl_weighted_jensen</x:v>
-      </x:c>
-      <x:c r="K1" s="29" t="str">
-        <x:v>sppr_jensen</x:v>
-      </x:c>
-      <x:c r="L1" s="29" t="str">
-        <x:v>ppr_jensen</x:v>
-      </x:c>
-      <x:c r="M1" s="29" t="str">
-        <x:v>jensen_difference</x:v>
-      </x:c>
-      <x:c r="N1" s="29" t="str">
-        <x:v>jensen_ratio_correct_to_error</x:v>
-      </x:c>
-      <x:c r="O1" s="29" t="str">
-        <x:v>jensen_percent_difference</x:v>
+        <x:v>ppr</x:v>
       </x:c>
     </x:row>
     <x:row r="2" ht="18" customHeight="1">
       <x:c r="A2" s="24" t="str">
         <x:v>Cephalopods</x:v>
       </x:c>
-      <x:c r="B2" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C2" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D2" s="31" t="n">
+      <x:c r="B2" s="31" t="n">
         <x:v>1507.3078119471995</x:v>
       </x:c>
+      <x:c r="C2" s="32" t="n">
+        <x:v>3.8452137449389867</x:v>
+      </x:c>
+      <x:c r="D2" s="32" t="n">
+        <x:f>IF(C2="","",(1/'Metadata'!$B$5)^(C2-1))</x:f>
+        <x:v>700.1865191495615</x:v>
+      </x:c>
       <x:c r="E2" s="31" t="n">
-        <x:v>1507.3078119471995</x:v>
-      </x:c>
-      <x:c r="F2" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G2" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H2" s="32" t="n">
-        <x:f>IF(E2=0,"",I2/E2)</x:f>
-        <x:v>740.7342790318656</x:v>
-      </x:c>
-      <x:c r="I2" s="31" t="n">
-        <x:f>IF(C2=0,"",SUMIF('Species'!$G$2:$G$195,A2,'Species'!$U$2:$U$195))</x:f>
-        <x:v>1116514.5653618078</x:v>
-      </x:c>
-      <x:c r="J2" s="32" t="n">
-        <x:v>3.8452137449389867</x:v>
-      </x:c>
-      <x:c r="K2" s="32" t="n">
-        <x:f>IF(J2="","",(1/'Metadata'!$B$5)^(J2-1))</x:f>
-        <x:v>700.1865191495615</x:v>
-      </x:c>
-      <x:c r="L2" s="31" t="n">
-        <x:f>IF(E2=0,"",E2*K2)</x:f>
+        <x:f>IF(B2=0,"",B2*D2)</x:f>
         <x:v>1055396.6101342514</x:v>
-      </x:c>
-      <x:c r="M2" s="31" t="n">
-        <x:f>IF(E2=0,"",I2-L2)</x:f>
-        <x:v>61117.955227556406</x:v>
-      </x:c>
-      <x:c r="N2" s="32" t="n">
-        <x:f>IF(L2=0,"",I2/L2)</x:f>
-        <x:v>1.0579099408134178</x:v>
-      </x:c>
-      <x:c r="O2" s="34" t="n">
-        <x:f>IF(L2=0,"",M2/L2)</x:f>
-        <x:v>0.057909940813417916</x:v>
       </x:c>
     </x:row>
     <x:row r="3" ht="18" customHeight="1">
       <x:c r="A3" s="24" t="str">
         <x:v>Large bathypelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C3" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D3" s="31" t="n">
+      <x:c r="B3" s="31" t="n">
         <x:v>1.0583852268</x:v>
       </x:c>
+      <x:c r="C3" s="32" t="n">
+        <x:v>4.34</x:v>
+      </x:c>
+      <x:c r="D3" s="32" t="n">
+        <x:f>IF(C3="","",(1/'Metadata'!$B$5)^(C3-1))</x:f>
+        <x:v>2187.761623949552</x:v>
+      </x:c>
       <x:c r="E3" s="31" t="n">
-        <x:v>1.0583852268</x:v>
-      </x:c>
-      <x:c r="F3" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G3" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H3" s="32" t="n">
-        <x:f>IF(E3=0,"",I3/E3)</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="I3" s="31" t="n">
-        <x:f>IF(C3=0,"",SUMIF('Species'!$G$2:$G$195,A3,'Species'!$U$2:$U$195))</x:f>
+        <x:f>IF(B3=0,"",B3*D3)</x:f>
         <x:v>2315.4945825481827</x:v>
-      </x:c>
-      <x:c r="J3" s="32" t="n">
-        <x:v>4.34</x:v>
-      </x:c>
-      <x:c r="K3" s="32" t="n">
-        <x:f>IF(J3="","",(1/'Metadata'!$B$5)^(J3-1))</x:f>
-        <x:v>2187.761623949552</x:v>
-      </x:c>
-      <x:c r="L3" s="31" t="n">
-        <x:f>IF(E3=0,"",E3*K3)</x:f>
-        <x:v>2315.4945825481827</x:v>
-      </x:c>
-      <x:c r="M3" s="31" t="n">
-        <x:f>IF(E3=0,"",I3-L3)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N3" s="32" t="n">
-        <x:f>IF(L3=0,"",I3/L3)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O3" s="34" t="n">
-        <x:f>IF(L3=0,"",M3/L3)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="4" ht="18" customHeight="1">
       <x:c r="A4" s="24" t="str">
         <x:v>Large benthopelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B4" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C4" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D4" s="31" t="n">
+      <x:c r="B4" s="31" t="n">
         <x:v>1416.8518305571</x:v>
       </x:c>
+      <x:c r="C4" s="32" t="n">
+        <x:v>4.418322367060446</x:v>
+      </x:c>
+      <x:c r="D4" s="32" t="n">
+        <x:f>IF(C4="","",(1/'Metadata'!$B$5)^(C4-1))</x:f>
+        <x:v>2620.1271482434086</x:v>
+      </x:c>
       <x:c r="E4" s="31" t="n">
-        <x:v>1416.8518305571</x:v>
-      </x:c>
-      <x:c r="F4" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G4" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H4" s="32" t="n">
-        <x:f>IF(E4=0,"",I4/E4)</x:f>
-        <x:v>2624.85326059457</x:v>
-      </x:c>
-      <x:c r="I4" s="31" t="n">
-        <x:f>IF(C4=0,"",SUMIF('Species'!$G$2:$G$195,A4,'Species'!$U$2:$U$195))</x:f>
-        <x:v>3719028.1472171894</x:v>
-      </x:c>
-      <x:c r="J4" s="32" t="n">
-        <x:v>4.418322367060446</x:v>
-      </x:c>
-      <x:c r="K4" s="32" t="n">
-        <x:f>IF(J4="","",(1/'Metadata'!$B$5)^(J4-1))</x:f>
-        <x:v>2620.1271482434086</x:v>
-      </x:c>
-      <x:c r="L4" s="31" t="n">
-        <x:f>IF(E4=0,"",E4*K4)</x:f>
+        <x:f>IF(B4=0,"",B4*D4)</x:f>
         <x:v>3712331.946281027</x:v>
-      </x:c>
-      <x:c r="M4" s="31" t="n">
-        <x:f>IF(E4=0,"",I4-L4)</x:f>
-        <x:v>6696.200936162379</x:v>
-      </x:c>
-      <x:c r="N4" s="32" t="n">
-        <x:f>IF(L4=0,"",I4/L4)</x:f>
-        <x:v>1.0018037721391997</x:v>
-      </x:c>
-      <x:c r="O4" s="34" t="n">
-        <x:f>IF(L4=0,"",M4/L4)</x:f>
-        <x:v>0.0018037721391996097</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="18" customHeight="1">
       <x:c r="A5" s="24" t="str">
         <x:v>Large demersals (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C5" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D5" s="31" t="n">
+      <x:c r="B5" s="31" t="n">
         <x:v>6367.099657480099</x:v>
       </x:c>
+      <x:c r="C5" s="32" t="n">
+        <x:v>3.808428805721323</x:v>
+      </x:c>
+      <x:c r="D5" s="32" t="n">
+        <x:f>IF(C5="","",(1/'Metadata'!$B$5)^(C5-1))</x:f>
+        <x:v>643.3225959053611</x:v>
+      </x:c>
       <x:c r="E5" s="31" t="n">
-        <x:v>6367.099657480099</x:v>
-      </x:c>
-      <x:c r="F5" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G5" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H5" s="32" t="n">
-        <x:f>IF(E5=0,"",I5/E5)</x:f>
-        <x:v>650.6305978837437</x:v>
-      </x:c>
-      <x:c r="I5" s="31" t="n">
-        <x:f>IF(C5=0,"",SUMIF('Species'!$G$2:$G$195,A5,'Species'!$U$2:$U$195))</x:f>
-        <x:v>4142629.8569316566</x:v>
-      </x:c>
-      <x:c r="J5" s="32" t="n">
-        <x:v>3.808428805721323</x:v>
-      </x:c>
-      <x:c r="K5" s="32" t="n">
-        <x:f>IF(J5="","",(1/'Metadata'!$B$5)^(J5-1))</x:f>
-        <x:v>643.3225959053611</x:v>
-      </x:c>
-      <x:c r="L5" s="31" t="n">
-        <x:f>IF(E5=0,"",E5*K5)</x:f>
+        <x:f>IF(B5=0,"",B5*D5)</x:f>
         <x:v>4096099.080038233</x:v>
-      </x:c>
-      <x:c r="M5" s="31" t="n">
-        <x:f>IF(E5=0,"",I5-L5)</x:f>
-        <x:v>46530.776893423405</x:v>
-      </x:c>
-      <x:c r="N5" s="32" t="n">
-        <x:f>IF(L5=0,"",I5/L5)</x:f>
-        <x:v>1.0113597781655685</x:v>
-      </x:c>
-      <x:c r="O5" s="34" t="n">
-        <x:f>IF(L5=0,"",M5/L5)</x:f>
-        <x:v>0.011359778165568466</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="18" customHeight="1">
       <x:c r="A6" s="24" t="str">
         <x:v>Large pelagics (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B6" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C6" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D6" s="31" t="n">
+      <x:c r="B6" s="31" t="n">
         <x:v>19305.907497257096</x:v>
       </x:c>
+      <x:c r="C6" s="32" t="n">
+        <x:v>4.422400031344898</x:v>
+      </x:c>
+      <x:c r="D6" s="32" t="n">
+        <x:f>IF(C6="","",(1/'Metadata'!$B$5)^(C6-1))</x:f>
+        <x:v>2644.843817744091</x:v>
+      </x:c>
       <x:c r="E6" s="31" t="n">
-        <x:v>19305.907497257096</x:v>
-      </x:c>
-      <x:c r="F6" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G6" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H6" s="32" t="n">
-        <x:f>IF(E6=0,"",I6/E6)</x:f>
-        <x:v>2650.0934215378816</x:v>
-      </x:c>
-      <x:c r="I6" s="31" t="n">
-        <x:f>IF(C6=0,"",SUMIF('Species'!$G$2:$G$195,A6,'Species'!$U$2:$U$195))</x:f>
-        <x:v>51162458.4552999</x:v>
-      </x:c>
-      <x:c r="J6" s="32" t="n">
-        <x:v>4.422400031344898</x:v>
-      </x:c>
-      <x:c r="K6" s="32" t="n">
-        <x:f>IF(J6="","",(1/'Metadata'!$B$5)^(J6-1))</x:f>
-        <x:v>2644.843817744091</x:v>
-      </x:c>
-      <x:c r="L6" s="31" t="n">
-        <x:f>IF(E6=0,"",E6*K6)</x:f>
+        <x:f>IF(B6=0,"",B6*D6)</x:f>
         <x:v>51061110.090059735</x:v>
-      </x:c>
-      <x:c r="M6" s="31" t="n">
-        <x:f>IF(E6=0,"",I6-L6)</x:f>
-        <x:v>101348.3652401641</x:v>
-      </x:c>
-      <x:c r="N6" s="32" t="n">
-        <x:f>IF(L6=0,"",I6/L6)</x:f>
-        <x:v>1.001984844533568</x:v>
-      </x:c>
-      <x:c r="O6" s="34" t="n">
-        <x:f>IF(L6=0,"",M6/L6)</x:f>
-        <x:v>0.001984844533567906</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="18" customHeight="1">
       <x:c r="A7" s="24" t="str">
         <x:v>Large rays (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="C7" s="33" t="n">
-        <x:v>5</x:v>
-      </x:c>
-      <x:c r="D7" s="31" t="n">
+      <x:c r="B7" s="31" t="n">
         <x:v>678.4036837221001</x:v>
       </x:c>
+      <x:c r="C7" s="32" t="n">
+        <x:v>3.4950599812145144</x:v>
+      </x:c>
+      <x:c r="D7" s="32" t="n">
+        <x:f>IF(C7="","",(1/'Metadata'!$B$5)^(C7-1))</x:f>
+        <x:v>312.651114554602</x:v>
+      </x:c>
       <x:c r="E7" s="31" t="n">
-        <x:v>678.4036837221001</x:v>
-      </x:c>
-      <x:c r="F7" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G7" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H7" s="32" t="n">
-        <x:f>IF(E7=0,"",I7/E7)</x:f>
-        <x:v>334.1444663903793</x:v>
-      </x:c>
-      <x:c r="I7" s="31" t="n">
-        <x:f>IF(C7=0,"",SUMIF('Species'!$G$2:$G$195,A7,'Species'!$U$2:$U$195))</x:f>
-        <x:v>226684.8368945888</x:v>
-      </x:c>
-      <x:c r="J7" s="32" t="n">
-        <x:v>3.4950599812145144</x:v>
-      </x:c>
-      <x:c r="K7" s="32" t="n">
-        <x:f>IF(J7="","",(1/'Metadata'!$B$5)^(J7-1))</x:f>
-        <x:v>312.651114554602</x:v>
-      </x:c>
-      <x:c r="L7" s="31" t="n">
-        <x:f>IF(E7=0,"",E7*K7)</x:f>
+        <x:f>IF(B7=0,"",B7*D7)</x:f>
         <x:v>212103.6678336623</x:v>
-      </x:c>
-      <x:c r="M7" s="31" t="n">
-        <x:f>IF(E7=0,"",I7-L7)</x:f>
-        <x:v>14581.169060926506</x:v>
-      </x:c>
-      <x:c r="N7" s="32" t="n">
-        <x:f>IF(L7=0,"",I7/L7)</x:f>
-        <x:v>1.0687454828568146</x:v>
-      </x:c>
-      <x:c r="O7" s="34" t="n">
-        <x:f>IF(L7=0,"",M7/L7)</x:f>
-        <x:v>0.06874548285681449</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="18" customHeight="1">
       <x:c r="A8" s="24" t="str">
         <x:v>Large reef assoc. fish (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="C8" s="33" t="n">
-        <x:v>8</x:v>
-      </x:c>
-      <x:c r="D8" s="31" t="n">
+      <x:c r="B8" s="31" t="n">
         <x:v>16.6868183389</x:v>
       </x:c>
+      <x:c r="C8" s="32" t="n">
+        <x:v>3.872763478420717</x:v>
+      </x:c>
+      <x:c r="D8" s="32" t="n">
+        <x:f>IF(C8="","",(1/'Metadata'!$B$5)^(C8-1))</x:f>
+        <x:v>746.0423448372607</x:v>
+      </x:c>
       <x:c r="E8" s="31" t="n">
-        <x:v>16.6868183389</x:v>
-      </x:c>
-      <x:c r="F8" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G8" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H8" s="32" t="n">
-        <x:f>IF(E8=0,"",I8/E8)</x:f>
-        <x:v>879.626845441309</x:v>
-      </x:c>
-      <x:c r="I8" s="31" t="n">
-        <x:f>IF(C8=0,"",SUMIF('Species'!$G$2:$G$195,A8,'Species'!$U$2:$U$195))</x:f>
-        <x:v>14678.17337589879</x:v>
-      </x:c>
-      <x:c r="J8" s="32" t="n">
-        <x:v>3.872763478420717</x:v>
-      </x:c>
-      <x:c r="K8" s="32" t="n">
-        <x:f>IF(J8="","",(1/'Metadata'!$B$5)^(J8-1))</x:f>
-        <x:v>746.0423448372607</x:v>
-      </x:c>
-      <x:c r="L8" s="31" t="n">
-        <x:f>IF(E8=0,"",E8*K8)</x:f>
+        <x:f>IF(B8=0,"",B8*D8)</x:f>
         <x:v>12449.073081426359</x:v>
-      </x:c>
-      <x:c r="M8" s="31" t="n">
-        <x:f>IF(E8=0,"",I8-L8)</x:f>
-        <x:v>2229.1002944724314</x:v>
-      </x:c>
-      <x:c r="N8" s="32" t="n">
-        <x:f>IF(L8=0,"",I8/L8)</x:f>
-        <x:v>1.1790575314236191</x:v>
-      </x:c>
-      <x:c r="O8" s="34" t="n">
-        <x:f>IF(L8=0,"",M8/L8)</x:f>
-        <x:v>0.17905753142361913</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="18" customHeight="1">
       <x:c r="A9" s="24" t="str">
         <x:v>Large sharks (&gt;=90 cm)</x:v>
       </x:c>
-      <x:c r="B9" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="C9" s="33" t="n">
-        <x:v>20</x:v>
-      </x:c>
-      <x:c r="D9" s="31" t="n">
+      <x:c r="B9" s="31" t="n">
         <x:v>847.3258353878001</x:v>
       </x:c>
+      <x:c r="C9" s="32" t="n">
+        <x:v>4.336652529126498</x:v>
+      </x:c>
+      <x:c r="D9" s="32" t="n">
+        <x:f>IF(C9="","",(1/'Metadata'!$B$5)^(C9-1))</x:f>
+        <x:v>2170.9635366011084</x:v>
+      </x:c>
       <x:c r="E9" s="31" t="n">
-        <x:v>847.3258353878001</x:v>
-      </x:c>
-      <x:c r="F9" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G9" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H9" s="32" t="n">
-        <x:f>IF(E9=0,"",I9/E9)</x:f>
-        <x:v>2237.068203750294</x:v>
-      </x:c>
-      <x:c r="I9" s="31" t="n">
-        <x:f>IF(C9=0,"",SUMIF('Species'!$G$2:$G$195,A9,'Species'!$U$2:$U$195))</x:f>
-        <x:v>1895525.6845622032</x:v>
-      </x:c>
-      <x:c r="J9" s="32" t="n">
-        <x:v>4.336652529126498</x:v>
-      </x:c>
-      <x:c r="K9" s="32" t="n">
-        <x:f>IF(J9="","",(1/'Metadata'!$B$5)^(J9-1))</x:f>
-        <x:v>2170.9635366011084</x:v>
-      </x:c>
-      <x:c r="L9" s="31" t="n">
-        <x:f>IF(E9=0,"",E9*K9)</x:f>
+        <x:f>IF(B9=0,"",B9*D9)</x:f>
         <x:v>1839513.492246987</x:v>
-      </x:c>
-      <x:c r="M9" s="31" t="n">
-        <x:f>IF(E9=0,"",I9-L9)</x:f>
-        <x:v>56012.192315216176</x:v>
-      </x:c>
-      <x:c r="N9" s="32" t="n">
-        <x:f>IF(L9=0,"",I9/L9)</x:f>
-        <x:v>1.0304494598986587</x:v>
-      </x:c>
-      <x:c r="O9" s="34" t="n">
-        <x:f>IF(L9=0,"",M9/L9)</x:f>
-        <x:v>0.030449459898658656</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="18" customHeight="1">
       <x:c r="A10" s="24" t="str">
         <x:v>Lobsters, crabs</x:v>
       </x:c>
-      <x:c r="B10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C10" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D10" s="31" t="n">
+      <x:c r="B10" s="31" t="n">
         <x:v>1.7643012404000002</x:v>
       </x:c>
+      <x:c r="C10" s="32" t="n">
+        <x:v>2.696164491649699</x:v>
+      </x:c>
+      <x:c r="D10" s="32" t="n">
+        <x:f>IF(C10="","",(1/'Metadata'!$B$5)^(C10-1))</x:f>
+        <x:v>49.67804444059311</x:v>
+      </x:c>
       <x:c r="E10" s="31" t="n">
-        <x:v>1.7643012404000002</x:v>
-      </x:c>
-      <x:c r="F10" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G10" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H10" s="32" t="n">
-        <x:f>IF(E10=0,"",I10/E10)</x:f>
-        <x:v>51.91381750015842</x:v>
-      </x:c>
-      <x:c r="I10" s="31" t="n">
-        <x:f>IF(C10=0,"",SUMIF('Species'!$G$2:$G$195,A10,'Species'!$U$2:$U$195))</x:f>
-        <x:v>91.59161260942875</x:v>
-      </x:c>
-      <x:c r="J10" s="32" t="n">
-        <x:v>2.696164491649699</x:v>
-      </x:c>
-      <x:c r="K10" s="32" t="n">
-        <x:f>IF(J10="","",(1/'Metadata'!$B$5)^(J10-1))</x:f>
-        <x:v>49.67804444059311</x:v>
-      </x:c>
-      <x:c r="L10" s="31" t="n">
-        <x:f>IF(E10=0,"",E10*K10)</x:f>
+        <x:f>IF(B10=0,"",B10*D10)</x:f>
         <x:v>87.64703542718476</x:v>
-      </x:c>
-      <x:c r="M10" s="31" t="n">
-        <x:f>IF(E10=0,"",I10-L10)</x:f>
-        <x:v>3.9445771822439895</x:v>
-      </x:c>
-      <x:c r="N10" s="32" t="n">
-        <x:f>IF(L10=0,"",I10/L10)</x:f>
-        <x:v>1.045005255032511</x:v>
-      </x:c>
-      <x:c r="O10" s="34" t="n">
-        <x:f>IF(L10=0,"",M10/L10)</x:f>
-        <x:v>0.04500525503251114</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="18" customHeight="1">
       <x:c r="A11" s="24" t="str">
         <x:v>Medium bathydemersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C11" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D11" s="31" t="n">
+      <x:c r="B11" s="31" t="n">
         <x:v>193.5839601436</x:v>
       </x:c>
+      <x:c r="C11" s="32" t="n">
+        <x:v>4.209448304324207</x:v>
+      </x:c>
+      <x:c r="D11" s="32" t="n">
+        <x:f>IF(C11="","",(1/'Metadata'!$B$5)^(C11-1))</x:f>
+        <x:v>1619.7511774645209</x:v>
+      </x:c>
       <x:c r="E11" s="31" t="n">
-        <x:v>193.5839601436</x:v>
-      </x:c>
-      <x:c r="F11" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G11" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H11" s="32" t="n">
-        <x:f>IF(E11=0,"",I11/E11)</x:f>
-        <x:v>2335.067577247709</x:v>
-      </x:c>
-      <x:c r="I11" s="31" t="n">
-        <x:f>IF(C11=0,"",SUMIF('Species'!$G$2:$G$195,A11,'Species'!$U$2:$U$195))</x:f>
-        <x:v>452031.6288065331</x:v>
-      </x:c>
-      <x:c r="J11" s="32" t="n">
-        <x:v>4.209448304324207</x:v>
-      </x:c>
-      <x:c r="K11" s="32" t="n">
-        <x:f>IF(J11="","",(1/'Metadata'!$B$5)^(J11-1))</x:f>
-        <x:v>1619.7511774645209</x:v>
-      </x:c>
-      <x:c r="L11" s="31" t="n">
-        <x:f>IF(E11=0,"",E11*K11)</x:f>
+        <x:f>IF(B11=0,"",B11*D11)</x:f>
         <x:v>313557.847380841</x:v>
-      </x:c>
-      <x:c r="M11" s="31" t="n">
-        <x:f>IF(E11=0,"",I11-L11)</x:f>
-        <x:v>138473.78142569214</x:v>
-      </x:c>
-      <x:c r="N11" s="32" t="n">
-        <x:f>IF(L11=0,"",I11/L11)</x:f>
-        <x:v>1.4416211636301506</x:v>
-      </x:c>
-      <x:c r="O11" s="34" t="n">
-        <x:f>IF(L11=0,"",M11/L11)</x:f>
-        <x:v>0.4416211636301505</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="18" customHeight="1">
       <x:c r="A12" s="24" t="str">
         <x:v>Medium bathypelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C12" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D12" s="31" t="n">
+      <x:c r="B12" s="31" t="n">
         <x:v>67.2016245641</x:v>
       </x:c>
+      <x:c r="C12" s="32" t="n">
+        <x:v>4.081536039515392</x:v>
+      </x:c>
+      <x:c r="D12" s="32" t="n">
+        <x:f>IF(C12="","",(1/'Metadata'!$B$5)^(C12-1))</x:f>
+        <x:v>1206.5242063089886</x:v>
+      </x:c>
       <x:c r="E12" s="31" t="n">
-        <x:v>67.2016245641</x:v>
-      </x:c>
-      <x:c r="F12" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G12" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H12" s="32" t="n">
-        <x:f>IF(E12=0,"",I12/E12)</x:f>
-        <x:v>1207.4690332274427</x:v>
-      </x:c>
-      <x:c r="I12" s="31" t="n">
-        <x:f>IF(C12=0,"",SUMIF('Species'!$G$2:$G$195,A12,'Species'!$U$2:$U$195))</x:f>
-        <x:v>81143.88064372739</x:v>
-      </x:c>
-      <x:c r="J12" s="32" t="n">
-        <x:v>4.081536039515392</x:v>
-      </x:c>
-      <x:c r="K12" s="32" t="n">
-        <x:f>IF(J12="","",(1/'Metadata'!$B$5)^(J12-1))</x:f>
-        <x:v>1206.5242063089886</x:v>
-      </x:c>
-      <x:c r="L12" s="31" t="n">
-        <x:f>IF(E12=0,"",E12*K12)</x:f>
+        <x:f>IF(B12=0,"",B12*D12)</x:f>
         <x:v>81080.38673987538</x:v>
-      </x:c>
-      <x:c r="M12" s="31" t="n">
-        <x:f>IF(E12=0,"",I12-L12)</x:f>
-        <x:v>63.49390385200968</x:v>
-      </x:c>
-      <x:c r="N12" s="32" t="n">
-        <x:f>IF(L12=0,"",I12/L12)</x:f>
-        <x:v>1.0007830981869352</x:v>
-      </x:c>
-      <x:c r="O12" s="34" t="n">
-        <x:f>IF(L12=0,"",M12/L12)</x:f>
-        <x:v>0.0007830981869353041</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="18" customHeight="1">
       <x:c r="A13" s="24" t="str">
         <x:v>Medium benthopelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B13" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="C13" s="33" t="n">
-        <x:v>22</x:v>
-      </x:c>
-      <x:c r="D13" s="31" t="n">
+      <x:c r="B13" s="31" t="n">
         <x:v>24560.844621935103</x:v>
       </x:c>
+      <x:c r="C13" s="32" t="n">
+        <x:v>3.597412985242826</x:v>
+      </x:c>
+      <x:c r="D13" s="32" t="n">
+        <x:f>IF(C13="","",(1/'Metadata'!$B$5)^(C13-1))</x:f>
+        <x:v>395.74276631339524</x:v>
+      </x:c>
       <x:c r="E13" s="31" t="n">
-        <x:v>24560.844621935103</x:v>
-      </x:c>
-      <x:c r="F13" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G13" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H13" s="32" t="n">
-        <x:f>IF(E13=0,"",I13/E13)</x:f>
-        <x:v>439.0302566093629</x:v>
-      </x:c>
-      <x:c r="I13" s="31" t="n">
-        <x:f>IF(C13=0,"",SUMIF('Species'!$G$2:$G$195,A13,'Species'!$U$2:$U$195))</x:f>
-        <x:v>10782953.916910859</x:v>
-      </x:c>
-      <x:c r="J13" s="32" t="n">
-        <x:v>3.597412985242826</x:v>
-      </x:c>
-      <x:c r="K13" s="32" t="n">
-        <x:f>IF(J13="","",(1/'Metadata'!$B$5)^(J13-1))</x:f>
-        <x:v>395.74276631339524</x:v>
-      </x:c>
-      <x:c r="L13" s="31" t="n">
-        <x:f>IF(E13=0,"",E13*K13)</x:f>
+        <x:f>IF(B13=0,"",B13*D13)</x:f>
         <x:v>9719776.593678074</x:v>
-      </x:c>
-      <x:c r="M13" s="31" t="n">
-        <x:f>IF(E13=0,"",I13-L13)</x:f>
-        <x:v>1063177.3232327849</x:v>
-      </x:c>
-      <x:c r="N13" s="32" t="n">
-        <x:f>IF(L13=0,"",I13/L13)</x:f>
-        <x:v>1.109382897125876</x:v>
-      </x:c>
-      <x:c r="O13" s="34" t="n">
-        <x:f>IF(L13=0,"",M13/L13)</x:f>
-        <x:v>0.10938289712587586</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="18" customHeight="1">
       <x:c r="A14" s="24" t="str">
         <x:v>Medium demersals (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B14" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C14" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D14" s="31" t="n">
+      <x:c r="B14" s="31" t="n">
         <x:v>112826.84428951557</x:v>
       </x:c>
+      <x:c r="C14" s="32" t="n">
+        <x:v>3.3722802178498585</x:v>
+      </x:c>
+      <x:c r="D14" s="32" t="n">
+        <x:f>IF(C14="","",(1/'Metadata'!$B$5)^(C14-1))</x:f>
+        <x:v>235.65693119432106</x:v>
+      </x:c>
       <x:c r="E14" s="31" t="n">
-        <x:v>112826.84428951557</x:v>
-      </x:c>
-      <x:c r="F14" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G14" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H14" s="32" t="n">
-        <x:f>IF(E14=0,"",I14/E14)</x:f>
-        <x:v>263.32093333593633</x:v>
-      </x:c>
-      <x:c r="I14" s="31" t="n">
-        <x:f>IF(C14=0,"",SUMIF('Species'!$G$2:$G$195,A14,'Species'!$U$2:$U$195))</x:f>
-        <x:v>29709669.943663597</x:v>
-      </x:c>
-      <x:c r="J14" s="32" t="n">
-        <x:v>3.3722802178498585</x:v>
-      </x:c>
-      <x:c r="K14" s="32" t="n">
-        <x:f>IF(J14="","",(1/'Metadata'!$B$5)^(J14-1))</x:f>
-        <x:v>235.65693119432106</x:v>
-      </x:c>
-      <x:c r="L14" s="31" t="n">
-        <x:f>IF(E14=0,"",E14*K14)</x:f>
+        <x:f>IF(B14=0,"",B14*D14)</x:f>
         <x:v>26588427.881606746</x:v>
-      </x:c>
-      <x:c r="M14" s="31" t="n">
-        <x:f>IF(E14=0,"",I14-L14)</x:f>
-        <x:v>3121242.0620568506</x:v>
-      </x:c>
-      <x:c r="N14" s="32" t="n">
-        <x:f>IF(L14=0,"",I14/L14)</x:f>
-        <x:v>1.117390997164449</x:v>
-      </x:c>
-      <x:c r="O14" s="34" t="n">
-        <x:f>IF(L14=0,"",M14/L14)</x:f>
-        <x:v>0.11739099716444887</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="18" customHeight="1">
       <x:c r="A15" s="24" t="str">
         <x:v>Medium pelagics (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B15" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="C15" s="33" t="n">
-        <x:v>21</x:v>
-      </x:c>
-      <x:c r="D15" s="31" t="n">
+      <x:c r="B15" s="31" t="n">
         <x:v>24717.328122337505</x:v>
       </x:c>
+      <x:c r="C15" s="32" t="n">
+        <x:v>3.6513234811685793</x:v>
+      </x:c>
+      <x:c r="D15" s="32" t="n">
+        <x:f>IF(C15="","",(1/'Metadata'!$B$5)^(C15-1))</x:f>
+        <x:v>448.04690448415147</x:v>
+      </x:c>
       <x:c r="E15" s="31" t="n">
-        <x:v>24717.328122337505</x:v>
-      </x:c>
-      <x:c r="F15" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G15" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H15" s="32" t="n">
-        <x:f>IF(E15=0,"",I15/E15)</x:f>
-        <x:v>772.8751476049069</x:v>
-      </x:c>
-      <x:c r="I15" s="31" t="n">
-        <x:f>IF(C15=0,"",SUMIF('Species'!$G$2:$G$195,A15,'Species'!$U$2:$U$195))</x:f>
-        <x:v>19103408.620950516</x:v>
-      </x:c>
-      <x:c r="J15" s="32" t="n">
-        <x:v>3.6513234811685793</x:v>
-      </x:c>
-      <x:c r="K15" s="32" t="n">
-        <x:f>IF(J15="","",(1/'Metadata'!$B$5)^(J15-1))</x:f>
-        <x:v>448.04690448415147</x:v>
-      </x:c>
-      <x:c r="L15" s="31" t="n">
-        <x:f>IF(E15=0,"",E15*K15)</x:f>
+        <x:f>IF(B15=0,"",B15*D15)</x:f>
         <x:v>11074522.352332383</x:v>
-      </x:c>
-      <x:c r="M15" s="31" t="n">
-        <x:f>IF(E15=0,"",I15-L15)</x:f>
-        <x:v>8028886.268618133</x:v>
-      </x:c>
-      <x:c r="N15" s="32" t="n">
-        <x:f>IF(L15=0,"",I15/L15)</x:f>
-        <x:v>1.7249871383326238</x:v>
-      </x:c>
-      <x:c r="O15" s="34" t="n">
-        <x:f>IF(L15=0,"",M15/L15)</x:f>
-        <x:v>0.7249871383326238</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="18" customHeight="1">
       <x:c r="A16" s="24" t="str">
         <x:v>Medium reef assoc. fish (30 - 89 cm)</x:v>
       </x:c>
-      <x:c r="B16" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="C16" s="33" t="n">
-        <x:v>11</x:v>
-      </x:c>
-      <x:c r="D16" s="31" t="n">
+      <x:c r="B16" s="31" t="n">
         <x:v>24722.564736048702</x:v>
       </x:c>
+      <x:c r="C16" s="32" t="n">
+        <x:v>3.3166821011097776</x:v>
+      </x:c>
+      <x:c r="D16" s="32" t="n">
+        <x:f>IF(C16="","",(1/'Metadata'!$B$5)^(C16-1))</x:f>
+        <x:v>207.33952588166528</x:v>
+      </x:c>
       <x:c r="E16" s="31" t="n">
-        <x:v>24722.564736048702</x:v>
-      </x:c>
-      <x:c r="F16" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G16" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H16" s="32" t="n">
-        <x:f>IF(E16=0,"",I16/E16)</x:f>
-        <x:v>287.0408710609496</x:v>
-      </x:c>
-      <x:c r="I16" s="31" t="n">
-        <x:f>IF(C16=0,"",SUMIF('Species'!$G$2:$G$195,A16,'Species'!$U$2:$U$195))</x:f>
-        <x:v>7096386.5166961355</x:v>
-      </x:c>
-      <x:c r="J16" s="32" t="n">
-        <x:v>3.3166821011097776</x:v>
-      </x:c>
-      <x:c r="K16" s="32" t="n">
-        <x:f>IF(J16="","",(1/'Metadata'!$B$5)^(J16-1))</x:f>
-        <x:v>207.33952588166528</x:v>
-      </x:c>
-      <x:c r="L16" s="31" t="n">
-        <x:f>IF(E16=0,"",E16*K16)</x:f>
+        <x:f>IF(B16=0,"",B16*D16)</x:f>
         <x:v>5125964.850951116</x:v>
-      </x:c>
-      <x:c r="M16" s="31" t="n">
-        <x:f>IF(E16=0,"",I16-L16)</x:f>
-        <x:v>1970421.66574502</x:v>
-      </x:c>
-      <x:c r="N16" s="32" t="n">
-        <x:f>IF(L16=0,"",I16/L16)</x:f>
-        <x:v>1.3844001515889073</x:v>
-      </x:c>
-      <x:c r="O16" s="34" t="n">
-        <x:f>IF(L16=0,"",M16/L16)</x:f>
-        <x:v>0.3844001515889074</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="18" customHeight="1">
       <x:c r="A17" s="24" t="str">
         <x:v>Other demersal invertebrates</x:v>
       </x:c>
-      <x:c r="B17" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C17" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D17" s="31" t="n">
+      <x:c r="B17" s="31" t="n">
         <x:v>308.9782732733</x:v>
       </x:c>
+      <x:c r="C17" s="32" t="n">
+        <x:v>2.0002266277792615</x:v>
+      </x:c>
+      <x:c r="D17" s="32" t="n">
+        <x:f>IF(C17="","",(1/'Metadata'!$B$5)^(C17-1))</x:f>
+        <x:v>10.00521965923014</x:v>
+      </x:c>
       <x:c r="E17" s="31" t="n">
-        <x:v>308.9782732733</x:v>
-      </x:c>
-      <x:c r="F17" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G17" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H17" s="32" t="n">
-        <x:f>IF(E17=0,"",I17/E17)</x:f>
-        <x:v>10.02033663613152</x:v>
-      </x:c>
-      <x:c r="I17" s="31" t="n">
-        <x:f>IF(C17=0,"",SUMIF('Species'!$G$2:$G$195,A17,'Species'!$U$2:$U$195))</x:f>
-        <x:v>3096.066311449104</x:v>
-      </x:c>
-      <x:c r="J17" s="32" t="n">
-        <x:v>2.0002266277792615</x:v>
-      </x:c>
-      <x:c r="K17" s="32" t="n">
-        <x:f>IF(J17="","",(1/'Metadata'!$B$5)^(J17-1))</x:f>
-        <x:v>10.00521965923014</x:v>
-      </x:c>
-      <x:c r="L17" s="31" t="n">
-        <x:f>IF(E17=0,"",E17*K17)</x:f>
+        <x:f>IF(B17=0,"",B17*D17)</x:f>
         <x:v>3091.395494029003</x:v>
-      </x:c>
-      <x:c r="M17" s="31" t="n">
-        <x:f>IF(E17=0,"",I17-L17)</x:f>
-        <x:v>4.670817420100775</x:v>
-      </x:c>
-      <x:c r="N17" s="32" t="n">
-        <x:f>IF(L17=0,"",I17/L17)</x:f>
-        <x:v>1.0015109090471026</x:v>
-      </x:c>
-      <x:c r="O17" s="34" t="n">
-        <x:f>IF(L17=0,"",M17/L17)</x:f>
-        <x:v>0.0015109090471026462</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="18" customHeight="1">
       <x:c r="A18" s="24" t="str">
         <x:v>Shrimps</x:v>
       </x:c>
-      <x:c r="B18" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="C18" s="33" t="n">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="D18" s="31" t="n">
+      <x:c r="B18" s="31" t="n">
         <x:v>61.66092358219999</x:v>
       </x:c>
+      <x:c r="C18" s="32" t="n">
+        <x:v>3.3336578989479833</x:v>
+      </x:c>
+      <x:c r="D18" s="32" t="n">
+        <x:f>IF(C18="","",(1/'Metadata'!$B$5)^(C18-1))</x:f>
+        <x:v>215.6045386930874</x:v>
+      </x:c>
       <x:c r="E18" s="31" t="n">
-        <x:v>61.66092358219999</x:v>
-      </x:c>
-      <x:c r="F18" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G18" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H18" s="32" t="n">
-        <x:f>IF(E18=0,"",I18/E18)</x:f>
-        <x:v>256.97069306058665</x:v>
-      </x:c>
-      <x:c r="I18" s="31" t="n">
-        <x:f>IF(C18=0,"",SUMIF('Species'!$G$2:$G$195,A18,'Species'!$U$2:$U$195))</x:f>
-        <x:v>15845.050267673803</x:v>
-      </x:c>
-      <x:c r="J18" s="32" t="n">
-        <x:v>3.3336578989479833</x:v>
-      </x:c>
-      <x:c r="K18" s="32" t="n">
-        <x:f>IF(J18="","",(1/'Metadata'!$B$5)^(J18-1))</x:f>
-        <x:v>215.6045386930874</x:v>
-      </x:c>
-      <x:c r="L18" s="31" t="n">
-        <x:f>IF(E18=0,"",E18*K18)</x:f>
+        <x:f>IF(B18=0,"",B18*D18)</x:f>
         <x:v>13294.374984329943</x:v>
-      </x:c>
-      <x:c r="M18" s="31" t="n">
-        <x:f>IF(E18=0,"",I18-L18)</x:f>
-        <x:v>2550.6752833438604</x:v>
-      </x:c>
-      <x:c r="N18" s="32" t="n">
-        <x:f>IF(L18=0,"",I18/L18)</x:f>
-        <x:v>1.191861241039939</x:v>
-      </x:c>
-      <x:c r="O18" s="34" t="n">
-        <x:f>IF(L18=0,"",M18/L18)</x:f>
-        <x:v>0.19186124103993885</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="18" customHeight="1">
       <x:c r="A19" s="24" t="str">
         <x:v>Small benthopelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C19" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D19" s="31" t="n">
+      <x:c r="B19" s="31" t="n">
         <x:v>88.2915331451</x:v>
       </x:c>
+      <x:c r="C19" s="32" t="n">
+        <x:v>3.27</x:v>
+      </x:c>
+      <x:c r="D19" s="32" t="n">
+        <x:f>IF(C19="","",(1/'Metadata'!$B$5)^(C19-1))</x:f>
+        <x:v>186.20871366628674</x:v>
+      </x:c>
       <x:c r="E19" s="31" t="n">
-        <x:v>88.2915331451</x:v>
-      </x:c>
-      <x:c r="F19" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G19" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H19" s="32" t="n">
-        <x:f>IF(E19=0,"",I19/E19)</x:f>
-        <x:v>186.20871366628677</x:v>
-      </x:c>
-      <x:c r="I19" s="31" t="n">
-        <x:f>IF(C19=0,"",SUMIF('Species'!$G$2:$G$195,A19,'Species'!$U$2:$U$195))</x:f>
+        <x:f>IF(B19=0,"",B19*D19)</x:f>
         <x:v>16440.652814573394</x:v>
-      </x:c>
-      <x:c r="J19" s="32" t="n">
-        <x:v>3.27</x:v>
-      </x:c>
-      <x:c r="K19" s="32" t="n">
-        <x:f>IF(J19="","",(1/'Metadata'!$B$5)^(J19-1))</x:f>
-        <x:v>186.20871366628674</x:v>
-      </x:c>
-      <x:c r="L19" s="31" t="n">
-        <x:f>IF(E19=0,"",E19*K19)</x:f>
-        <x:v>16440.652814573394</x:v>
-      </x:c>
-      <x:c r="M19" s="31" t="n">
-        <x:f>IF(E19=0,"",I19-L19)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N19" s="32" t="n">
-        <x:f>IF(L19=0,"",I19/L19)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O19" s="34" t="n">
-        <x:f>IF(L19=0,"",M19/L19)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="18" customHeight="1">
       <x:c r="A20" s="24" t="str">
         <x:v>Small demersals (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B20" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="C20" s="33" t="n">
-        <x:v>3</x:v>
-      </x:c>
-      <x:c r="D20" s="31" t="n">
+      <x:c r="B20" s="31" t="n">
         <x:v>7410.337262774</x:v>
       </x:c>
+      <x:c r="C20" s="32" t="n">
+        <x:v>3.0933625979185115</x:v>
+      </x:c>
+      <x:c r="D20" s="32" t="n">
+        <x:f>IF(C20="","",(1/'Metadata'!$B$5)^(C20-1))</x:f>
+        <x:v>123.98313052518438</x:v>
+      </x:c>
       <x:c r="E20" s="31" t="n">
-        <x:v>7410.337262774</x:v>
-      </x:c>
-      <x:c r="F20" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G20" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H20" s="32" t="n">
-        <x:f>IF(E20=0,"",I20/E20)</x:f>
-        <x:v>137.74304288870366</x:v>
-      </x:c>
-      <x:c r="I20" s="31" t="n">
-        <x:f>IF(C20=0,"",SUMIF('Species'!$G$2:$G$195,A20,'Species'!$U$2:$U$195))</x:f>
-        <x:v>1020722.4034060378</x:v>
-      </x:c>
-      <x:c r="J20" s="32" t="n">
-        <x:v>3.0933625979185115</x:v>
-      </x:c>
-      <x:c r="K20" s="32" t="n">
-        <x:f>IF(J20="","",(1/'Metadata'!$B$5)^(J20-1))</x:f>
-        <x:v>123.98313052518438</x:v>
-      </x:c>
-      <x:c r="L20" s="31" t="n">
-        <x:f>IF(E20=0,"",E20*K20)</x:f>
+        <x:f>IF(B20=0,"",B20*D20)</x:f>
         <x:v>918756.8120861463</x:v>
-      </x:c>
-      <x:c r="M20" s="31" t="n">
-        <x:f>IF(E20=0,"",I20-L20)</x:f>
-        <x:v>101965.59131989151</x:v>
-      </x:c>
-      <x:c r="N20" s="32" t="n">
-        <x:f>IF(L20=0,"",I20/L20)</x:f>
-        <x:v>1.1109821336599035</x:v>
-      </x:c>
-      <x:c r="O20" s="34" t="n">
-        <x:f>IF(L20=0,"",M20/L20)</x:f>
-        <x:v>0.11098213365990348</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="18" customHeight="1">
       <x:c r="A21" s="24" t="str">
         <x:v>Small pelagics (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="C21" s="33" t="n">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="D21" s="31" t="n">
+      <x:c r="B21" s="31" t="n">
         <x:v>14378.0958900467</x:v>
       </x:c>
+      <x:c r="C21" s="32" t="n">
+        <x:v>3.2238776775312212</x:v>
+      </x:c>
+      <x:c r="D21" s="32" t="n">
+        <x:f>IF(C21="","",(1/'Metadata'!$B$5)^(C21-1))</x:f>
+        <x:v>167.4471181576183</x:v>
+      </x:c>
       <x:c r="E21" s="31" t="n">
-        <x:v>14378.0958900467</x:v>
-      </x:c>
-      <x:c r="F21" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G21" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H21" s="32" t="n">
-        <x:f>IF(E21=0,"",I21/E21)</x:f>
-        <x:v>197.1195500582097</x:v>
-      </x:c>
-      <x:c r="I21" s="31" t="n">
-        <x:f>IF(C21=0,"",SUMIF('Species'!$G$2:$G$195,A21,'Species'!$U$2:$U$195))</x:f>
-        <x:v>2834203.7925397996</x:v>
-      </x:c>
-      <x:c r="J21" s="32" t="n">
-        <x:v>3.2238776775312212</x:v>
-      </x:c>
-      <x:c r="K21" s="32" t="n">
-        <x:f>IF(J21="","",(1/'Metadata'!$B$5)^(J21-1))</x:f>
-        <x:v>167.4471181576183</x:v>
-      </x:c>
-      <x:c r="L21" s="31" t="n">
-        <x:f>IF(E21=0,"",E21*K21)</x:f>
+        <x:f>IF(B21=0,"",B21*D21)</x:f>
         <x:v>2407570.7213822156</x:v>
-      </x:c>
-      <x:c r="M21" s="31" t="n">
-        <x:f>IF(E21=0,"",I21-L21)</x:f>
-        <x:v>426633.07115758397</x:v>
-      </x:c>
-      <x:c r="N21" s="32" t="n">
-        <x:f>IF(L21=0,"",I21/L21)</x:f>
-        <x:v>1.1772047929344516</x:v>
-      </x:c>
-      <x:c r="O21" s="34" t="n">
-        <x:f>IF(L21=0,"",M21/L21)</x:f>
-        <x:v>0.17720479293445168</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="18" customHeight="1">
       <x:c r="A22" s="24" t="str">
         <x:v>Small reef assoc. fish (&lt;30 cm)</x:v>
       </x:c>
-      <x:c r="B22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C22" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D22" s="31" t="n">
+      <x:c r="B22" s="31" t="n">
         <x:v>0.29544458630000003</x:v>
       </x:c>
+      <x:c r="C22" s="32" t="n">
+        <x:v>3.73</x:v>
+      </x:c>
+      <x:c r="D22" s="32" t="n">
+        <x:f>IF(C22="","",(1/'Metadata'!$B$5)^(C22-1))</x:f>
+        <x:v>537.0317963702527</x:v>
+      </x:c>
       <x:c r="E22" s="31" t="n">
-        <x:v>0.29544458630000003</x:v>
-      </x:c>
-      <x:c r="F22" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G22" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H22" s="32" t="n">
-        <x:f>IF(E22=0,"",I22/E22)</x:f>
-        <x:v>537.0317963702527</x:v>
-      </x:c>
-      <x:c r="I22" s="31" t="n">
-        <x:f>IF(C22=0,"",SUMIF('Species'!$G$2:$G$195,A22,'Species'!$U$2:$U$195))</x:f>
+        <x:f>IF(B22=0,"",B22*D22)</x:f>
         <x:v>158.66313690855515</x:v>
-      </x:c>
-      <x:c r="J22" s="32" t="n">
-        <x:v>3.73</x:v>
-      </x:c>
-      <x:c r="K22" s="32" t="n">
-        <x:f>IF(J22="","",(1/'Metadata'!$B$5)^(J22-1))</x:f>
-        <x:v>537.0317963702527</x:v>
-      </x:c>
-      <x:c r="L22" s="31" t="n">
-        <x:f>IF(E22=0,"",E22*K22)</x:f>
-        <x:v>158.66313690855515</x:v>
-      </x:c>
-      <x:c r="M22" s="31" t="n">
-        <x:f>IF(E22=0,"",I22-L22)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N22" s="32" t="n">
-        <x:f>IF(L22=0,"",I22/L22)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O22" s="34" t="n">
-        <x:f>IF(L22=0,"",M22/L22)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="18" customHeight="1">
       <x:c r="A23" s="24" t="str">
         <x:v>Small to medium flatfishes (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B23" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="C23" s="33" t="n">
-        <x:v>6</x:v>
-      </x:c>
-      <x:c r="D23" s="31" t="n">
+      <x:c r="B23" s="31" t="n">
         <x:v>79.46006172969999</x:v>
       </x:c>
+      <x:c r="C23" s="32" t="n">
+        <x:v>3.2338663354193593</x:v>
+      </x:c>
+      <x:c r="D23" s="32" t="n">
+        <x:f>IF(C23="","",(1/'Metadata'!$B$5)^(C23-1))</x:f>
+        <x:v>171.34298770595112</x:v>
+      </x:c>
       <x:c r="E23" s="31" t="n">
-        <x:v>79.46006172969999</x:v>
-      </x:c>
-      <x:c r="F23" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G23" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H23" s="32" t="n">
-        <x:f>IF(E23=0,"",I23/E23)</x:f>
-        <x:v>188.31443922836488</x:v>
-      </x:c>
-      <x:c r="I23" s="31" t="n">
-        <x:f>IF(C23=0,"",SUMIF('Species'!$G$2:$G$195,A23,'Species'!$U$2:$U$195))</x:f>
-        <x:v>14963.476965679709</x:v>
-      </x:c>
-      <x:c r="J23" s="32" t="n">
-        <x:v>3.2338663354193593</x:v>
-      </x:c>
-      <x:c r="K23" s="32" t="n">
-        <x:f>IF(J23="","",(1/'Metadata'!$B$5)^(J23-1))</x:f>
-        <x:v>171.34298770595112</x:v>
-      </x:c>
-      <x:c r="L23" s="31" t="n">
-        <x:f>IF(E23=0,"",E23*K23)</x:f>
+        <x:f>IF(B23=0,"",B23*D23)</x:f>
         <x:v>13614.924380066102</x:v>
-      </x:c>
-      <x:c r="M23" s="31" t="n">
-        <x:f>IF(E23=0,"",I23-L23)</x:f>
-        <x:v>1348.5525856136064</x:v>
-      </x:c>
-      <x:c r="N23" s="32" t="n">
-        <x:f>IF(L23=0,"",I23/L23)</x:f>
-        <x:v>1.0990495832344138</x:v>
-      </x:c>
-      <x:c r="O23" s="34" t="n">
-        <x:f>IF(L23=0,"",M23/L23)</x:f>
-        <x:v>0.09904958323441375</x:v>
       </x:c>
     </x:row>
     <x:row r="24" ht="18" customHeight="1">
       <x:c r="A24" s="24" t="str">
         <x:v>Small to medium rays (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B24" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="C24" s="33" t="n">
-        <x:v>2</x:v>
-      </x:c>
-      <x:c r="D24" s="31" t="n">
+      <x:c r="B24" s="31" t="n">
         <x:v>2.5086777252</x:v>
       </x:c>
+      <x:c r="C24" s="32" t="n">
+        <x:v>3.8</x:v>
+      </x:c>
+      <x:c r="D24" s="32" t="n">
+        <x:f>IF(C24="","",(1/'Metadata'!$B$5)^(C24-1))</x:f>
+        <x:v>630.957344480193</x:v>
+      </x:c>
       <x:c r="E24" s="31" t="n">
-        <x:v>2.5086777252</x:v>
-      </x:c>
-      <x:c r="F24" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G24" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H24" s="32" t="n">
-        <x:f>IF(E24=0,"",I24/E24)</x:f>
-        <x:v>630.957344480193</x:v>
-      </x:c>
-      <x:c r="I24" s="31" t="n">
-        <x:f>IF(C24=0,"",SUMIF('Species'!$G$2:$G$195,A24,'Species'!$U$2:$U$195))</x:f>
+        <x:f>IF(B24=0,"",B24*D24)</x:f>
         <x:v>1582.8686356488033</x:v>
-      </x:c>
-      <x:c r="J24" s="32" t="n">
-        <x:v>3.8</x:v>
-      </x:c>
-      <x:c r="K24" s="32" t="n">
-        <x:f>IF(J24="","",(1/'Metadata'!$B$5)^(J24-1))</x:f>
-        <x:v>630.957344480193</x:v>
-      </x:c>
-      <x:c r="L24" s="31" t="n">
-        <x:f>IF(E24=0,"",E24*K24)</x:f>
-        <x:v>1582.8686356488033</x:v>
-      </x:c>
-      <x:c r="M24" s="31" t="n">
-        <x:f>IF(E24=0,"",I24-L24)</x:f>
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="N24" s="32" t="n">
-        <x:f>IF(L24=0,"",I24/L24)</x:f>
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="O24" s="34" t="n">
-        <x:f>IF(L24=0,"",M24/L24)</x:f>
-        <x:v>0</x:v>
       </x:c>
     </x:row>
     <x:row r="25" ht="18" customHeight="1">
       <x:c r="A25" s="24" t="str">
         <x:v>Small to medium sharks (&lt;90 cm)</x:v>
       </x:c>
-      <x:c r="B25" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="C25" s="33" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="D25" s="31" t="n">
+      <x:c r="B25" s="31" t="n">
         <x:v>2.2373894655</x:v>
       </x:c>
+      <x:c r="C25" s="32" t="n">
+        <x:v>3.9699999999999998</x:v>
+      </x:c>
+      <x:c r="D25" s="32" t="n">
+        <x:f>IF(C25="","",(1/'Metadata'!$B$5)^(C25-1))</x:f>
+        <x:v>933.2543007969905</x:v>
+      </x:c>
       <x:c r="E25" s="31" t="n">
-        <x:v>2.2373894655</x:v>
-      </x:c>
-      <x:c r="F25" s="32" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="G25" s="34" t="n">
-        <x:v>1</x:v>
-      </x:c>
-      <x:c r="H25" s="32" t="n">
-        <x:f>IF(E25=0,"",I25/E25)</x:f>
-        <x:v>933.2543007969915</x:v>
-      </x:c>
-      <x:c r="I25" s="31" t="n">
-        <x:f>IF(C25=0,"",SUMIF('Species'!$G$2:$G$195,A25,'Species'!$U$2:$U$195))</x:f>
-        <x:v>2088.053341235757</x:v>
-      </x:c>
-      <x:c r="J25" s="32" t="n">
-        <x:v>3.9699999999999998</x:v>
-      </x:c>
-      <x:c r="K25" s="32" t="n">
-        <x:f>IF(J25="","",(1/'Metadata'!$B$5)^(J25-1))</x:f>
-        <x:v>933.2543007969905</x:v>
-      </x:c>
-      <x:c r="L25" s="31" t="n">
-        <x:f>IF(E25=0,"",E25*K25)</x:f>
+        <x:f>IF(B25=0,"",B25*D25)</x:f>
         <x:v>2088.053341235755</x:v>
       </x:c>
-      <x:c r="M25" s="31" t="n">
-        <x:f>IF(E25=0,"",I25-L25)</x:f>
-        <x:v>2.2737367544323206e-12</x:v>
-      </x:c>
-      <x:c r="N25" s="32" t="n">
-        <x:f>IF(L25=0,"",I25/L25)</x:f>
-        <x:v>1.000000000000001</x:v>
-      </x:c>
-      <x:c r="O25" s="34" t="n">
-        <x:f>IF(L25=0,"",M25/L25)</x:f>
-        <x:v>1.0889265659691789e-15</x:v>
-      </x:c>
     </x:row>
   </x:sheetData>
-  <x:conditionalFormatting sqref="G2:G25">
-    <x:cfRule type="cellIs" dxfId="2" priority="1" operator="lessThan">
-      <x:formula>0.9</x:formula>
-    </x:cfRule>
-  </x:conditionalFormatting>
-  <x:conditionalFormatting sqref="O2:O25">
-    <x:cfRule type="dataBar" priority="2">
-      <x:dataBar>
-        <x:cfvo type="min"/>
-        <x:cfvo type="max"/>
-        <x:color rgb="FFE28A32"/>
-      </x:dataBar>
-    </x:cfRule>
-  </x:conditionalFormatting>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rd11ea475acec4e5c"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R9a47c2afce054c5a"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -15937,7 +14558,7 @@
       <x:c r="B5" s="24" t="str">
         <x:v>catch_reconciled</x:v>
       </x:c>
-      <x:c r="C5" s="35" t="b">
+      <x:c r="C5" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D5" s="24" t="str">
@@ -16036,7 +14657,7 @@
         <x:v>commercial_ppr</x:v>
       </x:c>
       <x:c r="C12" s="24" t="n">
-        <x:v>133414622.34092882</x:v>
+        <x:v>119396344.3349186</x:v>
       </x:c>
       <x:c r="D12" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -16050,7 +14671,7 @@
         <x:v>functional_ppr</x:v>
       </x:c>
       <x:c r="C13" s="24" t="n">
-        <x:v>133414622.34092876</x:v>
+        <x:v>118271335.48023751</x:v>
       </x:c>
       <x:c r="D13" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -16064,7 +14685,7 @@
         <x:v>commercial_ppr_difference</x:v>
       </x:c>
       <x:c r="C14" s="24" t="n">
-        <x:v>2.9802322387695312e-8</x:v>
+        <x:v>-14018278.00601019</x:v>
       </x:c>
       <x:c r="D14" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -16078,7 +14699,7 @@
         <x:v>functional_ppr_difference</x:v>
       </x:c>
       <x:c r="C15" s="24" t="n">
-        <x:v>-2.9802322387695312e-8</x:v>
+        <x:v>-15143286.86069128</x:v>
       </x:c>
       <x:c r="D15" s="24" t="str">
         <x:v>tonnes_primary_production_equivalent</x:v>
@@ -16089,9 +14710,9 @@
         <x:v>EEZ_384</x:v>
       </x:c>
       <x:c r="B16" s="24" t="str">
-        <x:v>commercial_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C16" s="35" t="b">
+        <x:v>tl_coverage_complete</x:v>
+      </x:c>
+      <x:c r="C16" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D16" s="24" t="str">
@@ -16103,47 +14724,19 @@
         <x:v>EEZ_384</x:v>
       </x:c>
       <x:c r="B17" s="24" t="str">
-        <x:v>functional_ppr_reconciled</x:v>
-      </x:c>
-      <x:c r="C17" s="35" t="b">
+        <x:v>group_ppr_within_convexity_bound</x:v>
+      </x:c>
+      <x:c r="C17" s="33" t="b">
         <x:v>1</x:v>
       </x:c>
       <x:c r="D17" s="24" t="str">
         <x:v>boolean</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" ht="18" customHeight="1">
-      <x:c r="A18" s="24" t="str">
-        <x:v>EEZ_384</x:v>
-      </x:c>
-      <x:c r="B18" s="24" t="str">
-        <x:v>commercial_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C18" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D18" s="24" t="str">
-        <x:v>count</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" ht="18" customHeight="1">
-      <x:c r="A19" s="24" t="str">
-        <x:v>EEZ_384</x:v>
-      </x:c>
-      <x:c r="B19" s="24" t="str">
-        <x:v>functional_jensen_violations</x:v>
-      </x:c>
-      <x:c r="C19" s="24" t="n">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="D19" s="24" t="str">
-        <x:v>count</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <x:tableParts count="1">
-    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R3501d474520c4360"/>
+    <x:tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rfb21135e3a074222"/>
   </x:tableParts>
 </x:worksheet>
 </file>
@@ -16190,7 +14783,7 @@
       <x:c r="A5" s="22" t="str">
         <x:v>Transfer efficiency</x:v>
       </x:c>
-      <x:c r="B5" s="36" t="n">
+      <x:c r="B5" s="34" t="n">
         <x:v>0.1</x:v>
       </x:c>
       <x:c r="C5" s="18" t="str">
